--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -424,7 +424,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -452,7 +452,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -424,7 +424,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -905,7 +905,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>De'Yari</v>
+        <v>De&amp;apos;Yari</v>
       </c>
       <c r="B37" t="str">
         <v>Brown</v>
@@ -2980,7 +2980,7 @@
         <v>Dylan</v>
       </c>
       <c r="B185" t="str">
-        <v>O'Connell</v>
+        <v>O&amp;apos;Connell</v>
       </c>
       <c r="C185" t="str">
         <v>9</v>
@@ -2994,7 +2994,7 @@
         <v>Henry</v>
       </c>
       <c r="B186" t="str">
-        <v>O'Connor</v>
+        <v>O&amp;apos;Connor</v>
       </c>
       <c r="C186" t="str">
         <v>9</v>
@@ -3008,7 +3008,7 @@
         <v>Joshua</v>
       </c>
       <c r="B187" t="str">
-        <v>O'Connor</v>
+        <v>O&amp;apos;Connor</v>
       </c>
       <c r="C187" t="str">
         <v>9</v>
@@ -3022,7 +3022,7 @@
         <v>Jaxon</v>
       </c>
       <c r="B188" t="str">
-        <v>O'Hara</v>
+        <v>O&amp;apos;Hara</v>
       </c>
       <c r="C188" t="str">
         <v>9</v>
@@ -3036,7 +3036,7 @@
         <v>Keenan</v>
       </c>
       <c r="B189" t="str">
-        <v>O'Mahony</v>
+        <v>O&amp;apos;Mahony</v>
       </c>
       <c r="C189" t="str">
         <v>9</v>
@@ -10078,7 +10078,7 @@
         <v>Chase</v>
       </c>
       <c r="B692" t="str">
-        <v>O'Keefe</v>
+        <v>O&amp;apos;Keefe</v>
       </c>
       <c r="C692" t="str">
         <v>11</v>
@@ -10092,7 +10092,7 @@
         <v>Colin</v>
       </c>
       <c r="B693" t="str">
-        <v>O'Keeffe</v>
+        <v>O&amp;apos;Keeffe</v>
       </c>
       <c r="C693" t="str">
         <v>11</v>
@@ -11954,7 +11954,7 @@
         <v>Wyatt</v>
       </c>
       <c r="B826" t="str">
-        <v>D'Amato</v>
+        <v>D&amp;apos;Amato</v>
       </c>
       <c r="C826" t="str">
         <v>12</v>
